--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量算定の再検証_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量算定の再検証_20260925.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>総給付費1％＝月額57.9円</t>
+          <t>総給付費1％＝月額56.9円</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>**※ 差は-0.23％、保険料の月額で-13円。**従前6,224円に対し6,210円。100円未満切上げ後の6,300円は変わらない。</t>
+          <t>**※ 差は-0.23％、保険料の月額で-13円。**従前6,108円に対し6,095円。100円未満切上げ後の6,300円は変わらない。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量算定の再検証_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見込量算定の再検証_20260925.xlsx
@@ -1203,7 +1203,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>**※ 差は-0.23％、保険料の月額で-13円。**従前6,108円に対し6,095円。100円未満切上げ後の6,300円は変わらない。</t>
+          <t>**※ 差は-0.23％、保険料の月額で-13円。**従前6,061円に対し6,048円。100円未満切上げ後の6,100円は変わらない。</t>
         </is>
       </c>
     </row>
